--- a/contact_forms/046_seller_information_form--contact_forms.xlsx
+++ b/contact_forms/046_seller_information_form--contact_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,8 +665,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,12 +694,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option1':_'residential'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option1': 'Residential'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option2':_'commercial'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option2': 'Commercial'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option3':_'mixed'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option3': 'Mixed'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option1':_'need_to_move_out'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option1': 'Need to move out'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option2':_'other'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option2': 'Other'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option3':_'inheritance'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option3': 'Inheritance'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option1':_'morning'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option1': 'Morning'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option2':_'afternoon'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option2': 'Afternoon'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option3':_'evening'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option3': 'Evening'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option1':_'within_a_week'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option1': 'Within a week'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option2':_'in_a_month'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option2': 'In a month'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option3':_'in_a_few_months'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option3': 'In a few months'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option1':_'email'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option1': 'Email'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option2':_'phone'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option2': 'Phone'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option3':_'in_person'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option3': 'In Person'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
